--- a/对比脚本/表格/metrics_summary.xlsx
+++ b/对比脚本/表格/metrics_summary.xlsx
@@ -424,16 +424,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -482,622 +482,262 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>long_term_forecast_PatchGatedLSTM_672_24_Hog_parking_Jean_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl24_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_Exp_0</t>
+          <t>long_term_forecast_HotPlug_TimeMixer_504_24_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl24_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.06969023495912552</v>
+        <v>0.2821275889873505</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.154107078909874</v>
+        <v>0.3897360861301422</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.3178544640541077</v>
+        <v>2.642223119735718</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9468336030840874</v>
+        <v>0.7088617980480194</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.2639890811361817</v>
+        <v>0.5311568402904649</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4.201815128326416</v>
+        <v>690.0949096679688</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchGatedLSTM_672_24_Hog_parking_Jean_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl24_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_Exp_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_24_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl24_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>long_term_forecast_PatchGatedLSTM_672_48_Hog_parking_Jean_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl48_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_Exp_0</t>
+          <t>long_term_forecast_HotPlug_TimeMixer_504_24_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl24_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1194660887122154</v>
+        <v>0.2754822373390198</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.1945237517356873</v>
+        <v>0.3838098049163818</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.3915524780750275</v>
+        <v>2.592239379882812</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.907512903213501</v>
+        <v>0.7157194018363953</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3456386678486876</v>
+        <v>0.5248640179503828</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5.599458694458008</v>
+        <v>793.9266357421875</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchGatedLSTM_672_48_Hog_parking_Jean_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl48_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_Exp_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_24_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl24_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>long_term_forecast_PatchGatedLSTM_672_72_Hog_parking_Jean_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl72_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_Exp_0</t>
+          <t>long_term_forecast_HotPlug_TimeMixer_504_48_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl48_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1562215089797974</v>
+        <v>0.3373281955718994</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.2192047536373138</v>
+        <v>0.4261269867420197</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.4463174045085907</v>
+        <v>2.814949035644531</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8772933334112167</v>
+        <v>0.64985391497612</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.3952486672713741</v>
+        <v>0.5807996173999251</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6.81451416015625</v>
+        <v>713.3403930664062</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchGatedLSTM_672_72_Hog_parking_Jean_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl72_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_Exp_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_48_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl48_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>long_term_forecast_PatchGatedLSTM_672_96_Hog_parking_Jean_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl96_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_Exp_0</t>
+          <t>long_term_forecast_HotPlug_TimeMixer_504_48_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl48_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.1882562637329102</v>
+        <v>0.3267151117324829</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.2442122995853424</v>
+        <v>0.4228159785270691</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4950413405895233</v>
+        <v>2.845434188842773</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.8500778377056122</v>
+        <v>0.6608702838420868</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.4338850812518335</v>
+        <v>0.5715899856824671</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8.517024040222168</v>
+        <v>695.2259521484375</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchGatedLSTM_672_96_Hog_parking_Jean_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl96_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_Exp_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_48_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl48_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>long_term_forecast_PatchTST_Hog_parking_Jean_672_24_PatchTST_custom_ftMS_sl672_ll24_pl24_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
+          <t>long_term_forecast_HotPlug_TimeMixer_504_72_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl72_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.08153413123929601</v>
+        <v>0.3397516012191772</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.172781013534215</v>
+        <v>0.4324512779712677</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3090857449427195</v>
+        <v>3.102362871170044</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9378018230199814</v>
+        <v>0.6461031138896942</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.2855418204734571</v>
+        <v>0.5828821503693326</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.532777600591472</v>
+        <v>859.5532836914062</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchTST_Hog_parking_Jean_672_24_PatchTST_custom_ftMS_sl672_ll24_pl24_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_72_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl72_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>long_term_forecast_PatchTST_Hog_parking_Jean_672_48_PatchTST_custom_ftMS_sl672_ll24_pl48_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
+          <t>long_term_forecast_HotPlug_TimeMixer_504_72_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl72_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.1450245241442403</v>
+        <v>0.3483671247959137</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.2223310457149005</v>
+        <v>0.4393013715744019</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.3621496807373246</v>
+        <v>3.052369356155396</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8877352997660637</v>
+        <v>0.6371288597583771</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3808208557107138</v>
+        <v>0.5902263335330894</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2.99561971226296</v>
+        <v>784.0922241210938</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchTST_Hog_parking_Jean_672_48_PatchTST_custom_ftMS_sl672_ll24_pl48_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_72_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl72_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>long_term_forecast_PatchTST_Hog_parking_Jean_672_72_PatchTST_custom_ftMS_sl672_ll24_pl72_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
+          <t>long_term_forecast_HotPlug_TimeMixer_504_96_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl96_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.1754581679412911</v>
+        <v>0.3769264221191406</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.246414333830302</v>
+        <v>0.4593967199325562</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.4401854155632688</v>
+        <v>3.112890958786011</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8621943145990372</v>
+        <v>0.6064815521240234</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.418877270738448</v>
+        <v>0.6139433378734072</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5.454772396929581</v>
+        <v>764.2107543945312</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchTST_Hog_parking_Jean_672_72_PatchTST_custom_ftMS_sl672_ll24_pl72_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_96_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl96_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>long_term_forecast_PatchTST_Hog_parking_Jean_672_96_PatchTST_custom_ftMS_sl672_ll24_pl96_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
+          <t>long_term_forecast_HotPlug_TimeMixer_504_96_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl96_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.2344734529633487</v>
+        <v>0.4266076982021332</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.2841423625781671</v>
+        <v>0.4836199879646301</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.4204711477987838</v>
+        <v>3.576038837432861</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8132858723402023</v>
+        <v>0.5546133816242218</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.4842245893832207</v>
+        <v>0.6531521248546415</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3.50001165768165</v>
+        <v>1577.561279296875</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchTST_Hog_parking_Jean_672_96_PatchTST_custom_ftMS_sl672_ll24_pl96_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_96_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl96_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>long_term_forecast_TimeMixer_Hog_parking_Jean_672_24_TimeMixer_custom_ftMS_sl672_ll24_pl24_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>平均(全部实验)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.0825702605041157</v>
+        <v>0.3391632474958897</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.1708371707122009</v>
+        <v>0.4296572767198086</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.3747073960975085</v>
+        <v>2.967313468456268</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9370114132761955</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.2873504141359739</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>5.405226358278009</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_TimeMixer_Hog_parking_Jean_672_24_TimeMixer_custom_ftMS_sl672_ll24_pl24_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>long_term_forecast_TimeMixer_Hog_parking_Jean_672_48_TimeMixer_custom_ftMS_sl672_ll24_pl48_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0.1391851635669603</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.2134045995011592</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.507026591231183</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0.8922555893659592</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.3730752786864339</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>15.58015703628937</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_TimeMixer_Hog_parking_Jean_672_48_TimeMixer_custom_ftMS_sl672_ll24_pl48_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>long_term_forecast_TimeMixer_Hog_parking_Jean_672_72_TimeMixer_custom_ftMS_sl672_ll24_pl72_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>0.1945990994656776</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0.2534186121199817</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0.4618322478603876</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0.8471609205007553</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.441133879299332</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>5.602218205337913</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_TimeMixer_Hog_parking_Jean_672_72_TimeMixer_custom_ftMS_sl672_ll24_pl72_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>long_term_forecast_TimeMixer_Hog_parking_Jean_672_96_TimeMixer_custom_ftMS_sl672_ll24_pl96_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.2107500687924327</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>0.2671084472538582</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0.5681699078895851</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.8321771323680878</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.4590752321705373</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>10.70284598174061</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_TimeMixer_Hog_parking_Jean_672_96_TimeMixer_custom_ftMS_sl672_ll24_pl96_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>long_term_forecast_TimeXer_Hog_parking_Jean_672_24_TimeXer_custom_ftMS_sl672_ll24_pl24_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0.08289967636415023</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0.1618953296886414</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0.3293176183002254</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.9367601200938225</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.2879230389603274</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>5.071211410343766</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_TimeXer_Hog_parking_Jean_672_24_TimeXer_custom_ftMS_sl672_ll24_pl24_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>long_term_forecast_TimeXer_Hog_parking_Jean_672_48_TimeXer_custom_ftMS_sl672_ll24_pl48_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>0.1535559246238273</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>0.2233635421086943</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>0.4583738955015409</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.8811310529708862</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.3918621245078776</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>8.351057454258367</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_TimeXer_Hog_parking_Jean_672_48_TimeXer_custom_ftMS_sl672_ll24_pl48_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>long_term_forecast_TimeXer_Hog_parking_Jean_672_72_TimeXer_custom_ftMS_sl672_ll24_pl72_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>0.1690448206002897</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>0.233118948435454</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>0.5246804501185248</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.8672313690185547</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.4111506057399037</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>12.67797426756944</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_TimeXer_Hog_parking_Jean_672_72_TimeXer_custom_ftMS_sl672_ll24_pl72_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>long_term_forecast_TimeXer_Hog_parking_Jean_672_96_TimeXer_custom_ftMS_sl672_ll24_pl96_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>0.2152559024712922</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>0.2662124543282716</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>0.5986911229243526</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0.82858906686306</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0.4639567894441164</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>17.44469019391494</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_TimeXer_Hog_parking_Jean_672_96_TimeXer_custom_ftMS_sl672_ll24_pl96_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>long_term_forecast_iTransformer_Hog_parking_Jean_672_24_iTransformer_custom_ftMS_sl672_ll24_pl24_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>0.08875260715147321</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0.1767967140922276</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>0.3340142906502891</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0.9322952255606651</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0.2979137579090184</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>2.870537283103723</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_iTransformer_Hog_parking_Jean_672_24_iTransformer_custom_ftMS_sl672_ll24_pl24_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>long_term_forecast_iTransformer_Hog_parking_Jean_672_48_iTransformer_custom_ftMS_sl672_ll24_pl48_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0.1371841458984303</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0.2122330221834458</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>0.4298946540763246</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0.8938046097755432</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.3703837819052426</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>4.874615892507627</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_iTransformer_Hog_parking_Jean_672_48_iTransformer_custom_ftMS_sl672_ll24_pl48_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>long_term_forecast_iTransformer_Hog_parking_Jean_672_72_iTransformer_custom_ftMS_sl672_ll24_pl72_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>0.1770897113313177</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0.2455591082458577</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>0.4592920159082088</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0.8609129041433334</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0.420820283887692</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>5.155356213089815</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_iTransformer_Hog_parking_Jean_672_72_iTransformer_custom_ftMS_sl672_ll24_pl72_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>long_term_forecast_iTransformer_Hog_parking_Jean_672_96_iTransformer_custom_ftMS_sl672_ll24_pl96_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>0.2145101413279223</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0.2693170956939329</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>0.5080055238750336</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0.8291829526424408</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0.4631523953602338</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>6.20178624950812</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_iTransformer_Hog_parking_Jean_672_96_iTransformer_custom_ftMS_sl672_ll24_pl96_dm512_nh8_el2_dl1_df2048_expand2_dc4_fc1_ebtimeF_dtTrue_Exp_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>平均(全部实验)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>0.1517760947385057</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0.2215490841944764</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>0.4368331695351254</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0.8810623671859503</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>0.6474540382623672</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1118,7 +758,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1164,24 +804,24 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>assembly</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.08108938204363213</v>
+        <v>0.2788049131631851</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.1672834613874317</v>
+        <v>0.386772945523262</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.33299590280897</v>
+        <v>2.617231249809265</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.9381404370069504</v>
+        <v>0.7122905999422073</v>
       </c>
     </row>
     <row r="3">
@@ -1189,24 +829,24 @@
         <v>48</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>assembly</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1388831693891348</v>
+        <v>0.3320216536521912</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.2131711922487774</v>
+        <v>0.4244714826345444</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4297994599242801</v>
+        <v>2.830191612243652</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8924878910183907</v>
+        <v>0.6553620994091034</v>
       </c>
     </row>
     <row r="4">
@@ -1214,24 +854,24 @@
         <v>72</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>assembly</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.1744826616636747</v>
+        <v>0.3440593630075455</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2395431512537818</v>
+        <v>0.4358763247728348</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.4664615067917962</v>
+        <v>3.07736611366272</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8629585683345795</v>
+        <v>0.6416159868240356</v>
       </c>
     </row>
     <row r="5">
@@ -1239,24 +879,24 @@
         <v>96</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>assembly</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2126491658575812</v>
+        <v>0.4017670601606369</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.2661985318879144</v>
+        <v>0.4715083539485931</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.5180758086154557</v>
+        <v>3.344464898109436</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.8306625723838806</v>
+        <v>0.5805474668741226</v>
       </c>
     </row>
   </sheetData>

--- a/对比脚本/表格/metrics_summary.xlsx
+++ b/对比脚本/表格/metrics_summary.xlsx
@@ -424,16 +424,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -482,262 +482,142 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>long_term_forecast_HotPlug_TimeMixer_504_24_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl24_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
+          <t>long_term_forecast_PatchGatedLSTM_672_12_江苏_原始数据_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl12_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft1.0_seed42_Exp_0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2821275889873505</v>
+        <v>0.2577276229858398</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.3897360861301422</v>
+        <v>0.3494170308113098</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2.642223119735718</v>
+        <v>2.968591928482056</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.7088617980480194</v>
+        <v>0.81956547498703</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.5311568402904649</v>
+        <v>0.5076688123036907</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>690.0949096679688</v>
+        <v>3916.29296875</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_24_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl24_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchGatedLSTM_672_12_江苏_原始数据_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl12_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft1.0_seed42_Exp_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>long_term_forecast_HotPlug_TimeMixer_504_24_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl24_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
+          <t>long_term_forecast_PatchGatedLSTM_672_24_江苏_原始数据_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl24_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft1.0_seed42_Exp_0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2754822373390198</v>
+        <v>0.4323668777942657</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.3838098049163818</v>
+        <v>0.4588066041469574</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2.592239379882812</v>
+        <v>3.076622009277344</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7157194018363953</v>
+        <v>0.6988115906715393</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5248640179503828</v>
+        <v>0.6575461031701623</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>793.9266357421875</v>
+        <v>4345.77197265625</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_24_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl24_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchGatedLSTM_672_24_江苏_原始数据_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl24_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft1.0_seed42_Exp_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>long_term_forecast_HotPlug_TimeMixer_504_48_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl48_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
+          <t>long_term_forecast_PatchGatedLSTM_672_48_江苏_原始数据_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl48_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft1.0_seed42_Exp_0</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.3373281955718994</v>
+        <v>0.5463519096374512</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.4261269867420197</v>
+        <v>0.5293151140213013</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2.814949035644531</v>
+        <v>4.325149536132812</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.64985391497612</v>
+        <v>0.6171578764915466</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.5807996173999251</v>
+        <v>0.7391562146376442</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>713.3403930664062</v>
+        <v>10266.193359375</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_48_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl48_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchGatedLSTM_672_48_江苏_原始数据_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl48_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft1.0_seed42_Exp_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>long_term_forecast_HotPlug_TimeMixer_504_48_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl48_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
+          <t>long_term_forecast_PatchGatedLSTM_672_96_江苏_原始数据_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl96_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft1.0_seed42_Exp_0</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3267151117324829</v>
+        <v>0.5459722280502319</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.4228159785270691</v>
+        <v>0.53934645652771</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.845434188842773</v>
+        <v>5.386081695556641</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6608702838420868</v>
+        <v>0.6189463138580322</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.5715899856824671</v>
+        <v>0.7388993355324066</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>695.2259521484375</v>
+        <v>14417.8955078125</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_48_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl48_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
+          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_PatchGatedLSTM_672_96_江苏_原始数据_PatchGatedLSTM_BuildingEnergy_ftMS_sl672_ll24_pl96_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft1.0_seed42_Exp_0/metrics.npy</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>long_term_forecast_HotPlug_TimeMixer_504_72_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl72_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>平均(全部实验)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.3397516012191772</v>
+        <v>0.4456046596169472</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.4324512779712677</v>
+        <v>0.4692213013768196</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3.102362871170044</v>
+        <v>3.939111292362213</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.6461031138896942</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.5828821503693326</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>859.5532836914062</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_72_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl72_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>long_term_forecast_HotPlug_TimeMixer_504_72_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl72_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0.3483671247959137</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0.4393013715744019</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>3.052369356155396</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.6371288597583771</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.5902263335330894</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>784.0922241210938</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_72_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl72_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>long_term_forecast_HotPlug_TimeMixer_504_96_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl96_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>0.3769264221191406</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0.4593967199325562</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>3.112890958786011</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.6064815521240234</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.6139433378734072</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>764.2107543945312</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_96_Hog_assembly_Colette_HotPlug_timemixer_baseline_only_BuildingEnergy_sl504_ll24_pl96_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>long_term_forecast_HotPlug_TimeMixer_504_96_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl96_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0.4266076982021332</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0.4836199879646301</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>3.576038837432861</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.5546133816242218</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.6531521248546415</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1577.561279296875</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>/home/ykj/build/Time-Series-Library/results/long_term_forecast_HotPlug_TimeMixer_504_96_Hog_assembly_Colette_HotPlug_timemixer_residual_BuildingEnergy_sl504_ll24_pl96_bpl16_bdm128_plen24_pstride12_topkp8_hs8_mdim128_lstm1_fft0.5_seed42_HotPlug_0/metrics.npy</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>平均(全部实验)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0.3391632474958897</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.4296572767198086</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>2.967313468456268</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0.6474540382623672</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>0.688620314002037</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -756,10 +636,10 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,100 +684,36 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>assembly</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.2788049131631851</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.386772945523262</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2.617231249809265</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.7122905999422073</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>48</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>assembly</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.3320216536521912</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.4244714826345444</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>2.830191612243652</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.6553620994091034</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>72</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>assembly</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.3440593630075455</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.4358763247728348</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.07736611366272</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.6416159868240356</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>96</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>assembly</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.4017670601606369</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.4715083539485931</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.344464898109436</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.5805474668741226</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
